--- a/thaco/color/1_Office_color_DATA_Mid Cycle.xlsx
+++ b/thaco/color/1_Office_color_DATA_Mid Cycle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2502B50F-CE20-734C-A044-8F7AF6EE7CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B7D12D-DE09-DE41-876D-366BA629EED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="3940" windowWidth="38360" windowHeight="20720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương tạm ứng kỳ 1" sheetId="3" r:id="rId1"/>
@@ -4196,7 +4196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
   <si>
     <t>Actual work day month</t>
   </si>
@@ -4352,9 +4352,6 @@
   </si>
   <si>
     <t>PC Seconded</t>
-  </si>
-  <si>
-    <t>PC seniority</t>
   </si>
   <si>
     <t>To Thanh Liem</t>
@@ -4860,235 +4857,232 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5466,1460 +5460,1383 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:BC20"/>
+  <dimension ref="A1:BB20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="86" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="87" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="89" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="5.5" style="89" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="90" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="13.6640625" style="91" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" style="92" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="21" width="7.1640625" style="93" customWidth="1"/>
-    <col min="22" max="29" width="12.33203125" style="91" customWidth="1"/>
-    <col min="30" max="30" width="13" style="91" customWidth="1"/>
-    <col min="31" max="31" width="6.6640625" style="91" customWidth="1"/>
-    <col min="32" max="43" width="10.5" style="91" customWidth="1"/>
-    <col min="44" max="48" width="12.6640625" style="91" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="50" width="10.6640625" style="94" customWidth="1" outlineLevel="1"/>
-    <col min="51" max="51" width="19.5" style="95" customWidth="1"/>
-    <col min="52" max="52" width="12.33203125" style="95" customWidth="1"/>
-    <col min="53" max="53" width="12.5" style="95" customWidth="1"/>
-    <col min="54" max="54" width="11.6640625" style="95" customWidth="1"/>
-    <col min="55" max="55" width="9.1640625" style="95" customWidth="1"/>
-    <col min="56" max="16384" width="9.1640625" style="95"/>
+    <col min="1" max="1" width="8.5" style="53" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="56" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="5.5" style="56" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="5.5" style="57" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="13.6640625" style="58" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" style="59" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="21" width="7.1640625" style="60" customWidth="1"/>
+    <col min="22" max="29" width="12.33203125" style="58" customWidth="1"/>
+    <col min="30" max="30" width="13" style="58" customWidth="1"/>
+    <col min="31" max="31" width="6.6640625" style="58" customWidth="1"/>
+    <col min="32" max="43" width="10.5" style="58" customWidth="1"/>
+    <col min="44" max="47" width="12.6640625" style="58" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="49" width="10.6640625" style="61" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="19.5" style="62" customWidth="1"/>
+    <col min="51" max="51" width="12.33203125" style="62" customWidth="1"/>
+    <col min="52" max="52" width="12.5" style="62" customWidth="1"/>
+    <col min="53" max="53" width="11.6640625" style="62" customWidth="1"/>
+    <col min="54" max="54" width="9.1640625" style="62" customWidth="1"/>
+    <col min="55" max="16384" width="9.1640625" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="9" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="10"/>
-      <c r="AL1" s="10"/>
-      <c r="AM1" s="10"/>
-      <c r="AN1" s="10"/>
-      <c r="AO1" s="10"/>
-      <c r="AP1" s="10"/>
-      <c r="AQ1" s="10"/>
-      <c r="AR1" s="7"/>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7"/>
-      <c r="AU1" s="7"/>
-      <c r="AV1" s="7"/>
-      <c r="AW1" s="8"/>
-      <c r="AX1" s="8"/>
+    <row r="1" spans="1:54" s="1" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
     </row>
-    <row r="2" spans="1:55" s="9" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="10"/>
-      <c r="AN2" s="10"/>
-      <c r="AO2" s="10"/>
-      <c r="AP2" s="10"/>
-      <c r="AQ2" s="10"/>
-      <c r="AR2" s="7"/>
-      <c r="AS2" s="7"/>
-      <c r="AT2" s="7"/>
-      <c r="AU2" s="7"/>
-      <c r="AV2" s="7"/>
-      <c r="AW2" s="8"/>
-      <c r="AX2" s="8"/>
+    <row r="2" spans="1:54" s="1" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="81"/>
+      <c r="AS2" s="81"/>
+      <c r="AT2" s="81"/>
+      <c r="AU2" s="81"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2"/>
     </row>
-    <row r="3" spans="1:55" s="9" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="12"/>
-      <c r="AF3" s="12"/>
-      <c r="AG3" s="12"/>
-      <c r="AH3" s="12"/>
-      <c r="AI3" s="12"/>
-      <c r="AJ3" s="12"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="12"/>
-      <c r="AM3" s="12"/>
-      <c r="AN3" s="12"/>
-      <c r="AO3" s="12"/>
-      <c r="AP3" s="12"/>
-      <c r="AQ3" s="12"/>
-      <c r="AR3" s="7"/>
-      <c r="AS3" s="7"/>
-      <c r="AT3" s="7"/>
-      <c r="AU3" s="7"/>
-      <c r="AV3" s="7"/>
-      <c r="AW3" s="8"/>
-      <c r="AX3" s="8"/>
+    <row r="3" spans="1:54" s="1" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="81"/>
+      <c r="AS3" s="81"/>
+      <c r="AT3" s="81"/>
+      <c r="AU3" s="81"/>
+      <c r="AV3" s="2"/>
+      <c r="AW3" s="2"/>
     </row>
-    <row r="4" spans="1:55" s="9" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="15"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="14"/>
-      <c r="AH4" s="15"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="15"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="15"/>
-      <c r="AN4" s="15"/>
-      <c r="AO4" s="14"/>
-      <c r="AP4" s="14"/>
-      <c r="AQ4" s="14"/>
-      <c r="AR4" s="19"/>
-      <c r="AS4" s="19"/>
-      <c r="AT4" s="19"/>
-      <c r="AU4" s="19"/>
-      <c r="AV4" s="19"/>
-      <c r="AW4" s="18"/>
-      <c r="AX4" s="18"/>
+    <row r="4" spans="1:54" s="1" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
+      <c r="AH4" s="8"/>
+      <c r="AI4" s="8"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="7"/>
+      <c r="AP4" s="7"/>
+      <c r="AQ4" s="7"/>
+      <c r="AR4" s="12"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="12"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
     </row>
-    <row r="5" spans="1:55" s="33" customFormat="1" ht="19.25" customHeight="1" collapsed="1">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:54" s="13" customFormat="1" ht="19.25" customHeight="1" collapsed="1">
+      <c r="A5" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="F5" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="71" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC5" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD5" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE5" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF5" s="69"/>
+      <c r="AG5" s="69"/>
+      <c r="AH5" s="69"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="69"/>
+      <c r="AK5" s="69"/>
+      <c r="AL5" s="69"/>
+      <c r="AM5" s="69"/>
+      <c r="AN5" s="69"/>
+      <c r="AO5" s="72"/>
+      <c r="AP5" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ5" s="78"/>
+      <c r="AR5" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS5" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT5" s="87"/>
+      <c r="AU5" s="87"/>
+      <c r="AV5" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW5" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="BA5" s="14"/>
+      <c r="BB5" s="14"/>
+    </row>
+    <row r="6" spans="1:54" s="13" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="S6" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="78"/>
+      <c r="U6" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" s="84" t="s">
+        <v>33</v>
+      </c>
+      <c r="W6" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="69"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="69"/>
+      <c r="AJ6" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK6" s="69"/>
+      <c r="AL6" s="69"/>
+      <c r="AM6" s="69"/>
+      <c r="AN6" s="69"/>
+      <c r="AO6" s="72"/>
+      <c r="AP6" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ6" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR6" s="90"/>
+      <c r="AS6" s="88"/>
+      <c r="AT6" s="89"/>
+      <c r="AU6" s="89"/>
+      <c r="AV6" s="65"/>
+      <c r="AW6" s="65"/>
+      <c r="BA6" s="14"/>
+      <c r="BB6" s="14"/>
+    </row>
+    <row r="7" spans="1:54" s="15" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="79"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
+      <c r="AE7" s="65"/>
+      <c r="AF7" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG7" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH7" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI7" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ7" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK7" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL7" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM7" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN7" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO7" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP7" s="65"/>
+      <c r="AQ7" s="65"/>
+      <c r="AR7" s="90"/>
+      <c r="AS7" s="91"/>
+      <c r="AT7" s="92"/>
+      <c r="AU7" s="92"/>
+      <c r="AV7" s="65"/>
+      <c r="AW7" s="65"/>
+      <c r="AX7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="14"/>
+      <c r="BB7" s="14"/>
+    </row>
+    <row r="8" spans="1:54" s="15" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="T8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="U8" s="68"/>
+      <c r="V8" s="68"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+      <c r="Z8" s="68"/>
+      <c r="AA8" s="68"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="68"/>
+      <c r="AD8" s="68"/>
+      <c r="AE8" s="68"/>
+      <c r="AF8" s="68"/>
+      <c r="AG8" s="68"/>
+      <c r="AH8" s="68"/>
+      <c r="AI8" s="68"/>
+      <c r="AJ8" s="68"/>
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="68"/>
+      <c r="AM8" s="68"/>
+      <c r="AN8" s="68"/>
+      <c r="AO8" s="68"/>
+      <c r="AP8" s="68"/>
+      <c r="AQ8" s="68"/>
+      <c r="AR8" s="93"/>
+      <c r="AS8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="AV8" s="66"/>
+      <c r="AW8" s="66"/>
+      <c r="AX8" s="1">
+        <v>25</v>
+      </c>
+      <c r="AY8" s="18"/>
+      <c r="BA8" s="14"/>
+      <c r="BB8" s="14"/>
+    </row>
+    <row r="9" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A9" s="24">
+        <v>2405236</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="19">
+        <v>9520000</v>
+      </c>
+      <c r="G9" s="27">
+        <v>1</v>
+      </c>
+      <c r="H9" s="28">
+        <v>11</v>
+      </c>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28">
+        <v>2</v>
+      </c>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28">
+        <v>0</v>
+      </c>
+      <c r="P9" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28">
+        <v>0</v>
+      </c>
+      <c r="S9" s="28">
+        <v>0</v>
+      </c>
+      <c r="T9" s="28">
+        <v>0</v>
+      </c>
+      <c r="U9" s="28">
+        <v>0</v>
+      </c>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29">
         <v>3</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC5" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="25"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS5" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="AT5" s="31"/>
-      <c r="AU5" s="31"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="AX5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BB5" s="34"/>
-      <c r="BC5" s="34"/>
-    </row>
-    <row r="6" spans="1:55" s="33" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="28"/>
-      <c r="U6" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
-      <c r="AM6" s="25"/>
-      <c r="AN6" s="25"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ6" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="4"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="3"/>
-      <c r="AX6" s="3"/>
-      <c r="BB6" s="34"/>
-      <c r="BC6" s="34"/>
-    </row>
-    <row r="7" spans="1:55" s="46" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG7" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH7" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI7" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ7" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK7" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL7" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM7" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN7" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP7" s="3"/>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="38"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="44"/>
-      <c r="AU7" s="44"/>
-      <c r="AV7" s="45"/>
-      <c r="AW7" s="3"/>
-      <c r="AX7" s="3"/>
-      <c r="AY7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="34"/>
-      <c r="BC7" s="34"/>
-    </row>
-    <row r="8" spans="1:55" s="46" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="T8" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="6"/>
-      <c r="AM8" s="6"/>
-      <c r="AN8" s="6"/>
-      <c r="AO8" s="6"/>
-      <c r="AP8" s="6"/>
-      <c r="AQ8" s="6"/>
-      <c r="AR8" s="45"/>
-      <c r="AS8" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="AT8" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="AU8" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="AV8" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="AW8" s="50"/>
-      <c r="AX8" s="50"/>
-      <c r="AY8" s="9">
-        <v>25</v>
-      </c>
-      <c r="AZ8" s="51"/>
-      <c r="BB8" s="34"/>
-      <c r="BC8" s="34"/>
-    </row>
-    <row r="9" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A9" s="57">
-        <v>2405236</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="52">
-        <v>9520000</v>
-      </c>
-      <c r="G9" s="60">
-        <v>1</v>
-      </c>
-      <c r="H9" s="61">
-        <v>11</v>
-      </c>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61">
-        <v>2</v>
-      </c>
-      <c r="M9" s="61"/>
-      <c r="N9" s="61"/>
-      <c r="O9" s="61">
-        <v>0</v>
-      </c>
-      <c r="P9" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="61">
-        <v>0</v>
-      </c>
-      <c r="S9" s="61">
-        <v>0</v>
-      </c>
-      <c r="T9" s="61">
-        <v>0</v>
-      </c>
-      <c r="U9" s="61">
-        <v>0</v>
-      </c>
-      <c r="V9" s="52"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="52"/>
-      <c r="AA9" s="52"/>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF9" s="62"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62">
-        <v>3</v>
-      </c>
-      <c r="AI9" s="62" t="e">
+      <c r="AI9" s="29" t="e">
         <f>#REF!-#REF!-AF9+AG9-AH9*4400000-IF(D9="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="62"/>
-      <c r="AL9" s="62">
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29">
         <v>0</v>
       </c>
-      <c r="AM9" s="62"/>
-      <c r="AN9" s="62"/>
-      <c r="AO9" s="62"/>
-      <c r="AP9" s="62"/>
-      <c r="AQ9" s="62"/>
-      <c r="AR9" s="54">
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="29"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="21">
         <v>60000000</v>
       </c>
-      <c r="AS9" s="55">
+      <c r="AS9" s="22">
         <v>0</v>
       </c>
-      <c r="AT9" s="55"/>
-      <c r="AU9" s="55"/>
-      <c r="AV9" s="55">
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="22"/>
+      <c r="AV9" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW9" s="22"/>
+      <c r="AX9" s="30"/>
+      <c r="AY9" s="31"/>
+      <c r="AZ9" s="31"/>
+      <c r="BA9" s="32"/>
+      <c r="BB9" s="32"/>
+    </row>
+    <row r="10" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A10" s="24">
+        <v>2106723</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="19">
+        <v>8480000</v>
+      </c>
+      <c r="G10" s="27">
+        <v>1</v>
+      </c>
+      <c r="H10" s="28">
+        <v>10.5</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28">
+        <v>2</v>
+      </c>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28">
         <v>0</v>
       </c>
-      <c r="AW9" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX9" s="55"/>
-      <c r="AY9" s="63"/>
-      <c r="AZ9" s="64"/>
-      <c r="BA9" s="64"/>
-      <c r="BB9" s="65"/>
-      <c r="BC9" s="65"/>
-    </row>
-    <row r="10" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A10" s="57">
-        <v>2106723</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="P10" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28">
+        <v>0</v>
+      </c>
+      <c r="S10" s="28">
+        <v>0</v>
+      </c>
+      <c r="T10" s="28">
+        <v>0</v>
+      </c>
+      <c r="U10" s="28">
+        <v>0</v>
+      </c>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="52">
-        <v>8480000</v>
-      </c>
-      <c r="G10" s="60">
-        <v>1</v>
-      </c>
-      <c r="H10" s="61">
-        <v>10.5</v>
-      </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61">
-        <v>2</v>
-      </c>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61">
-        <v>0</v>
-      </c>
-      <c r="P10" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61">
-        <v>0</v>
-      </c>
-      <c r="S10" s="61">
-        <v>0</v>
-      </c>
-      <c r="T10" s="61">
-        <v>0</v>
-      </c>
-      <c r="U10" s="61">
-        <v>0</v>
-      </c>
-      <c r="V10" s="52"/>
-      <c r="W10" s="52"/>
-      <c r="X10" s="52"/>
-      <c r="Y10" s="52"/>
-      <c r="Z10" s="52"/>
-      <c r="AA10" s="52"/>
-      <c r="AB10" s="52"/>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62" t="e">
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29" t="e">
         <f>#REF!-#REF!-AF10+AG10-AH10*4400000-IF(D10="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="62">
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29">
         <v>0</v>
       </c>
-      <c r="AM10" s="62"/>
-      <c r="AN10" s="62"/>
-      <c r="AO10" s="62"/>
-      <c r="AP10" s="62"/>
-      <c r="AQ10" s="62"/>
-      <c r="AR10" s="54">
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="29"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="21">
         <v>40000000</v>
       </c>
-      <c r="AS10" s="55">
+      <c r="AS10" s="22">
         <v>0</v>
       </c>
-      <c r="AT10" s="55">
+      <c r="AT10" s="22">
         <v>0</v>
       </c>
-      <c r="AU10" s="55"/>
-      <c r="AV10" s="55">
-        <f t="shared" ref="AV10:AV15" si="0">+AR10*5%</f>
-        <v>2000000</v>
-      </c>
-      <c r="AW10" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX10" s="55"/>
-      <c r="AY10" s="63"/>
-      <c r="AZ10" s="64"/>
-      <c r="BA10" s="64"/>
-      <c r="BB10" s="65"/>
-      <c r="BC10" s="65"/>
+      <c r="AU10" s="22"/>
+      <c r="AV10" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW10" s="22"/>
+      <c r="AX10" s="30"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="32"/>
+      <c r="BB10" s="32"/>
     </row>
-    <row r="11" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A11" s="66" t="s">
+    <row r="11" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A11" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="C11" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="F11" s="19">
+        <v>7820000</v>
+      </c>
+      <c r="G11" s="27">
+        <v>1</v>
+      </c>
+      <c r="H11" s="28">
+        <v>11</v>
+      </c>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28">
+        <v>2</v>
+      </c>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28">
+        <v>4</v>
+      </c>
+      <c r="P11" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28">
+        <v>0</v>
+      </c>
+      <c r="S11" s="28">
+        <v>0</v>
+      </c>
+      <c r="T11" s="28">
+        <v>0</v>
+      </c>
+      <c r="U11" s="28">
+        <v>0</v>
+      </c>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="52">
-        <v>7820000</v>
-      </c>
-      <c r="G11" s="60">
-        <v>1</v>
-      </c>
-      <c r="H11" s="61">
-        <v>11</v>
-      </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61">
-        <v>2</v>
-      </c>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61">
-        <v>4</v>
-      </c>
-      <c r="P11" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61">
-        <v>0</v>
-      </c>
-      <c r="S11" s="61">
-        <v>0</v>
-      </c>
-      <c r="T11" s="61">
-        <v>0</v>
-      </c>
-      <c r="U11" s="61">
-        <v>0</v>
-      </c>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62" t="e">
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29" t="e">
         <f>#REF!-#REF!-AF11+AG11-AH11*4400000-IF(D11="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="62"/>
-      <c r="AL11" s="62">
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29">
         <v>0</v>
       </c>
-      <c r="AM11" s="62"/>
-      <c r="AN11" s="62"/>
-      <c r="AO11" s="62"/>
-      <c r="AP11" s="62"/>
-      <c r="AQ11" s="62"/>
-      <c r="AR11" s="54">
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="29"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="21">
         <v>40000000</v>
       </c>
-      <c r="AS11" s="55">
+      <c r="AS11" s="22">
         <v>0</v>
       </c>
-      <c r="AT11" s="55">
+      <c r="AT11" s="22">
         <v>0</v>
       </c>
-      <c r="AU11" s="55"/>
-      <c r="AV11" s="55">
-        <f t="shared" si="0"/>
-        <v>2000000</v>
-      </c>
-      <c r="AW11" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX11" s="55"/>
-      <c r="AY11" s="63"/>
-      <c r="AZ11" s="64"/>
-      <c r="BA11" s="64"/>
-      <c r="BB11" s="65"/>
-      <c r="BC11" s="65"/>
+      <c r="AU11" s="22"/>
+      <c r="AV11" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW11" s="22"/>
+      <c r="AX11" s="30"/>
+      <c r="AY11" s="31"/>
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="32"/>
+      <c r="BB11" s="32"/>
     </row>
-    <row r="12" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A12" s="57">
+    <row r="12" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A12" s="24">
         <v>2406198</v>
       </c>
-      <c r="B12" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="53" t="s">
+      <c r="B12" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="E12" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="F12" s="19">
+        <v>6990000</v>
+      </c>
+      <c r="G12" s="27">
+        <v>1</v>
+      </c>
+      <c r="H12" s="28">
+        <v>10.5</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28">
+        <v>2</v>
+      </c>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28">
+        <v>0</v>
+      </c>
+      <c r="P12" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28">
+        <v>0</v>
+      </c>
+      <c r="S12" s="28">
+        <v>0</v>
+      </c>
+      <c r="T12" s="28">
+        <v>0</v>
+      </c>
+      <c r="U12" s="28">
+        <v>0</v>
+      </c>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="52">
-        <v>6990000</v>
-      </c>
-      <c r="G12" s="60">
-        <v>1</v>
-      </c>
-      <c r="H12" s="61">
-        <v>10.5</v>
-      </c>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61">
-        <v>2</v>
-      </c>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61">
-        <v>0</v>
-      </c>
-      <c r="P12" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="61"/>
-      <c r="R12" s="61">
-        <v>0</v>
-      </c>
-      <c r="S12" s="61">
-        <v>0</v>
-      </c>
-      <c r="T12" s="61">
-        <v>0</v>
-      </c>
-      <c r="U12" s="61">
-        <v>0</v>
-      </c>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="52"/>
-      <c r="AA12" s="52"/>
-      <c r="AB12" s="52"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF12" s="62"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62" t="e">
+      <c r="AF12" s="29"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="29" t="e">
         <f>#REF!-#REF!-AF12+AG12-AH12*4400000-IF(D12="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
-      <c r="AL12" s="62">
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="29"/>
+      <c r="AL12" s="29">
         <v>0</v>
       </c>
-      <c r="AM12" s="62"/>
-      <c r="AN12" s="62"/>
-      <c r="AO12" s="62"/>
-      <c r="AP12" s="62"/>
-      <c r="AQ12" s="62"/>
-      <c r="AR12" s="54">
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="29"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="21">
         <v>23000000</v>
       </c>
-      <c r="AS12" s="55">
+      <c r="AS12" s="22">
         <v>0</v>
       </c>
-      <c r="AT12" s="55">
+      <c r="AT12" s="22">
         <v>0</v>
       </c>
-      <c r="AU12" s="55"/>
-      <c r="AV12" s="55">
-        <f t="shared" si="0"/>
-        <v>1150000</v>
-      </c>
-      <c r="AW12" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX12" s="55"/>
-      <c r="AY12" s="63"/>
-      <c r="AZ12" s="64"/>
-      <c r="BA12" s="64"/>
-      <c r="BB12" s="65"/>
-      <c r="BC12" s="65"/>
+      <c r="AU12" s="22"/>
+      <c r="AV12" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW12" s="22"/>
+      <c r="AX12" s="30"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="32"/>
+      <c r="BB12" s="32"/>
     </row>
-    <row r="13" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A13" s="66" t="s">
+    <row r="13" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A13" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="C13" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="D13" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="52">
+      <c r="F13" s="19">
         <v>4850000</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="27">
         <v>1</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="28">
         <v>11</v>
       </c>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61">
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28">
         <v>2</v>
       </c>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61">
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28">
         <v>4</v>
       </c>
-      <c r="P13" s="61">
+      <c r="P13" s="28">
         <v>0</v>
       </c>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61">
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28">
         <v>0</v>
       </c>
-      <c r="S13" s="61">
+      <c r="S13" s="28">
         <v>0</v>
       </c>
-      <c r="T13" s="61">
+      <c r="T13" s="28">
         <v>0</v>
       </c>
-      <c r="U13" s="61">
+      <c r="U13" s="28">
         <v>0</v>
       </c>
-      <c r="V13" s="52"/>
-      <c r="W13" s="52"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="52"/>
-      <c r="AA13" s="52"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="52"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62" t="e">
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29" t="e">
         <f>#REF!-#REF!-AF13+AG13-AH13*4400000-IF(D13="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="62">
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29">
         <v>0</v>
       </c>
-      <c r="AM13" s="62"/>
-      <c r="AN13" s="62"/>
-      <c r="AO13" s="62"/>
-      <c r="AP13" s="62"/>
-      <c r="AQ13" s="62"/>
-      <c r="AR13" s="54">
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="29"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="21">
         <v>11000000</v>
       </c>
-      <c r="AS13" s="55">
+      <c r="AS13" s="22">
         <v>0</v>
       </c>
-      <c r="AT13" s="55">
+      <c r="AT13" s="22">
         <v>0</v>
       </c>
-      <c r="AU13" s="55"/>
-      <c r="AV13" s="55">
-        <f t="shared" si="0"/>
-        <v>550000</v>
-      </c>
-      <c r="AW13" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX13" s="55"/>
-      <c r="AY13" s="63"/>
-      <c r="AZ13" s="64"/>
-      <c r="BA13" s="64"/>
-      <c r="BB13" s="65"/>
-      <c r="BC13" s="65"/>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW13" s="22"/>
+      <c r="AX13" s="30"/>
+      <c r="AY13" s="31"/>
+      <c r="AZ13" s="31"/>
+      <c r="BA13" s="32"/>
+      <c r="BB13" s="32"/>
     </row>
-    <row r="14" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A14" s="57">
+    <row r="14" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A14" s="24">
         <v>2406145</v>
       </c>
-      <c r="B14" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="59" t="s">
+      <c r="B14" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="F14" s="19">
+        <v>6340000</v>
+      </c>
+      <c r="G14" s="27">
+        <v>1</v>
+      </c>
+      <c r="H14" s="28">
+        <v>10.5</v>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28">
+        <v>2</v>
+      </c>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28">
+        <v>0</v>
+      </c>
+      <c r="P14" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28">
+        <v>0</v>
+      </c>
+      <c r="S14" s="28">
+        <v>0</v>
+      </c>
+      <c r="T14" s="28">
+        <v>0</v>
+      </c>
+      <c r="U14" s="28">
+        <v>0</v>
+      </c>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
+      <c r="AC14" s="19"/>
+      <c r="AD14" s="19"/>
+      <c r="AE14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="52">
-        <v>6340000</v>
-      </c>
-      <c r="G14" s="60">
-        <v>1</v>
-      </c>
-      <c r="H14" s="61">
-        <v>10.5</v>
-      </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61">
-        <v>2</v>
-      </c>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61">
-        <v>0</v>
-      </c>
-      <c r="P14" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61">
-        <v>0</v>
-      </c>
-      <c r="S14" s="61">
-        <v>0</v>
-      </c>
-      <c r="T14" s="61">
-        <v>0</v>
-      </c>
-      <c r="U14" s="61">
-        <v>0</v>
-      </c>
-      <c r="V14" s="52"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="52"/>
-      <c r="Y14" s="52"/>
-      <c r="Z14" s="52"/>
-      <c r="AA14" s="52"/>
-      <c r="AB14" s="52"/>
-      <c r="AC14" s="52"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62" t="e">
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29" t="e">
         <f>#REF!-#REF!-AF14+AG14-AH14*4400000-IF(D14="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62">
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="29">
         <v>0</v>
       </c>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="62"/>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="62"/>
-      <c r="AR14" s="54">
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="29"/>
+      <c r="AO14" s="29"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="29"/>
+      <c r="AR14" s="21">
         <v>23000000</v>
       </c>
-      <c r="AS14" s="55">
+      <c r="AS14" s="22">
         <v>0</v>
       </c>
-      <c r="AT14" s="55">
+      <c r="AT14" s="22">
         <v>0</v>
       </c>
-      <c r="AU14" s="55"/>
-      <c r="AV14" s="55">
-        <f t="shared" si="0"/>
-        <v>1150000</v>
-      </c>
-      <c r="AW14" s="55" t="s">
+      <c r="AU14" s="22"/>
+      <c r="AV14" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW14" s="22"/>
+      <c r="AX14" s="30"/>
+      <c r="AY14" s="31"/>
+      <c r="AZ14" s="31"/>
+      <c r="BA14" s="32"/>
+      <c r="BB14" s="32"/>
+    </row>
+    <row r="15" spans="1:54" s="23" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A15" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="AX14" s="55"/>
-      <c r="AY14" s="63"/>
-      <c r="AZ14" s="64"/>
-      <c r="BA14" s="64"/>
-      <c r="BB14" s="65"/>
-      <c r="BC14" s="65"/>
-    </row>
-    <row r="15" spans="1:55" s="56" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="66" t="s">
+      <c r="B15" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="C15" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="F15" s="19">
+        <v>6340000</v>
+      </c>
+      <c r="G15" s="27">
+        <v>1</v>
+      </c>
+      <c r="H15" s="28">
+        <v>11</v>
+      </c>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28">
+        <v>2</v>
+      </c>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28">
+        <v>4</v>
+      </c>
+      <c r="P15" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28">
+        <v>0</v>
+      </c>
+      <c r="S15" s="28">
+        <v>0</v>
+      </c>
+      <c r="T15" s="28">
+        <v>0</v>
+      </c>
+      <c r="U15" s="28">
+        <v>0</v>
+      </c>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="52">
-        <v>6340000</v>
-      </c>
-      <c r="G15" s="60">
-        <v>1</v>
-      </c>
-      <c r="H15" s="61">
-        <v>11</v>
-      </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61">
-        <v>2</v>
-      </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61">
-        <v>4</v>
-      </c>
-      <c r="P15" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61">
-        <v>0</v>
-      </c>
-      <c r="S15" s="61">
-        <v>0</v>
-      </c>
-      <c r="T15" s="61">
-        <v>0</v>
-      </c>
-      <c r="U15" s="61">
-        <v>0</v>
-      </c>
-      <c r="V15" s="52"/>
-      <c r="W15" s="52"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="52"/>
-      <c r="Z15" s="52"/>
-      <c r="AA15" s="52"/>
-      <c r="AB15" s="52"/>
-      <c r="AC15" s="52"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62" t="e">
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29" t="e">
         <f>#REF!-#REF!-AF15+AG15-AH15*4400000-IF(D15="CT",11000000,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62">
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="29">
         <v>0</v>
       </c>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="62"/>
-      <c r="AR15" s="54">
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="29"/>
+      <c r="AO15" s="29"/>
+      <c r="AP15" s="29"/>
+      <c r="AQ15" s="29"/>
+      <c r="AR15" s="21">
         <v>17000000</v>
       </c>
-      <c r="AS15" s="55">
+      <c r="AS15" s="22">
         <v>0</v>
       </c>
-      <c r="AT15" s="55">
+      <c r="AT15" s="22">
         <v>0</v>
       </c>
-      <c r="AU15" s="55"/>
-      <c r="AV15" s="55">
-        <f t="shared" si="0"/>
-        <v>850000</v>
-      </c>
-      <c r="AW15" s="55" t="s">
+      <c r="AU15" s="22"/>
+      <c r="AV15" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW15" s="22"/>
+      <c r="AX15" s="30"/>
+      <c r="AY15" s="31"/>
+      <c r="AZ15" s="31"/>
+      <c r="BA15" s="32"/>
+      <c r="BB15" s="32"/>
+    </row>
+    <row r="16" spans="1:54" s="34" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="40"/>
+      <c r="AO16" s="40"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="40"/>
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="41"/>
+      <c r="AY16" s="42"/>
+    </row>
+    <row r="17" spans="1:51" s="43" customFormat="1" ht="21" customHeight="1">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="44"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="44"/>
+      <c r="Z17" s="44"/>
+      <c r="AA17" s="44"/>
+      <c r="AB17" s="44"/>
+      <c r="AC17" s="44"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="44"/>
+      <c r="AF17" s="48"/>
+      <c r="AG17" s="48"/>
+      <c r="AK17" s="44"/>
+      <c r="AL17" s="44"/>
+      <c r="AM17" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="AX15" s="55"/>
-      <c r="AY15" s="63"/>
-      <c r="AZ15" s="64"/>
-      <c r="BA15" s="64"/>
-      <c r="BB15" s="65"/>
-      <c r="BC15" s="65"/>
+      <c r="AN17" s="44"/>
+      <c r="AO17" s="44"/>
+      <c r="AP17" s="44"/>
+      <c r="AQ17" s="44"/>
+      <c r="AR17" s="49"/>
+      <c r="AS17" s="49"/>
+      <c r="AT17" s="49"/>
+      <c r="AU17" s="49"/>
     </row>
-    <row r="16" spans="1:55" s="67" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A16" s="68"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="72"/>
-      <c r="AM16" s="73"/>
-      <c r="AN16" s="73"/>
-      <c r="AO16" s="73"/>
-      <c r="AP16" s="73"/>
-      <c r="AQ16" s="73"/>
-      <c r="AR16" s="74"/>
-      <c r="AS16" s="74"/>
-      <c r="AT16" s="74"/>
-      <c r="AU16" s="74"/>
-      <c r="AV16" s="74"/>
-      <c r="AZ16" s="75"/>
+    <row r="18" spans="1:51" s="43" customFormat="1" ht="18" customHeight="1">
+      <c r="A18" s="50"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="46"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="51"/>
+      <c r="AD18" s="44"/>
+      <c r="AE18" s="44"/>
+      <c r="AK18" s="44"/>
+      <c r="AL18" s="48"/>
+      <c r="AR18" s="49"/>
+      <c r="AS18" s="49"/>
+      <c r="AT18" s="49"/>
+      <c r="AU18" s="49"/>
+      <c r="AY18" s="52"/>
     </row>
-    <row r="17" spans="1:52" s="76" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="77"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="R17" s="80"/>
-      <c r="S17" s="79"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="77"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-      <c r="Z17" s="77"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="77"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AK17" s="77"/>
-      <c r="AL17" s="77"/>
-      <c r="AM17" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN17" s="77"/>
-      <c r="AO17" s="77"/>
-      <c r="AP17" s="77"/>
-      <c r="AQ17" s="77"/>
-      <c r="AR17" s="82"/>
-      <c r="AS17" s="82"/>
-      <c r="AT17" s="82"/>
-      <c r="AU17" s="82"/>
-      <c r="AV17" s="82"/>
+    <row r="19" spans="1:51" ht="15" customHeight="1">
+      <c r="C19" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="U19" s="58"/>
+      <c r="AU19" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY19" s="63"/>
     </row>
-    <row r="18" spans="1:52" s="76" customFormat="1" ht="18" customHeight="1">
-      <c r="A18" s="83"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="80"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="79"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="AD18" s="77"/>
-      <c r="AE18" s="77"/>
-      <c r="AK18" s="77"/>
-      <c r="AL18" s="81"/>
-      <c r="AR18" s="82"/>
-      <c r="AS18" s="82"/>
-      <c r="AT18" s="82"/>
-      <c r="AU18" s="82"/>
-      <c r="AV18" s="82"/>
-      <c r="AZ18" s="85"/>
-    </row>
-    <row r="19" spans="1:52" ht="15" customHeight="1">
-      <c r="C19" s="88" t="s">
-        <v>81</v>
-      </c>
-      <c r="U19" s="91"/>
-      <c r="AU19" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="AZ19" s="96"/>
-    </row>
-    <row r="20" spans="1:52" ht="73.5" customHeight="1">
-      <c r="G20" s="93"/>
-      <c r="U20" s="91"/>
+    <row r="20" spans="1:51" ht="73.5" customHeight="1">
+      <c r="G20" s="60"/>
+      <c r="U20" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AE5:AE8"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AJ6:AO6"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="AL7:AL8"/>
-    <mergeCell ref="Y5:Y8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="AM7:AM8"/>
-    <mergeCell ref="AO7:AO8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="S6:T7"/>
-    <mergeCell ref="AR1:AV3"/>
-    <mergeCell ref="AC5:AC8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AD5:AD8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="H5:U5"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AF5:AO5"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AS5:AV7"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="AR5:AR8"/>
     <mergeCell ref="AP5:AQ5"/>
@@ -6936,17 +6853,52 @@
     <mergeCell ref="U6:U8"/>
     <mergeCell ref="AF6:AI6"/>
     <mergeCell ref="AB5:AB8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AF5:AO5"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AS5:AU7"/>
+    <mergeCell ref="AR1:AU3"/>
+    <mergeCell ref="AC5:AC8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AD5:AD8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AP6:AP8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="H5:U5"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AE5:AE8"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AJ6:AO6"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AQ6:AQ8"/>
+    <mergeCell ref="AL7:AL8"/>
+    <mergeCell ref="Y5:Y8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="AM7:AM8"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="S6:T7"/>
+    <mergeCell ref="AF7:AF8"/>
   </mergeCells>
-  <conditionalFormatting sqref="A16:A1048576 A1:A8">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  <conditionalFormatting sqref="A9:A15">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A1048576 A1:A8">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A15">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
